--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נריה ביבי - משהו בי נשבר קאבר</v>
+        <v>תאי חבאני - נווה הדרים קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410778&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410855&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נריה ביבי - משהו בי נשבר קאבר</v>
+        <v>תאי חבאני - נווה הדרים קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נועם דדון - הלב צמא קאבר</v>
+        <v>קסם בל - רולקס &amp; קסקט קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410777&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410854&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נועם דדון - הלב צמא קאבר</v>
+        <v>קסם בל - רולקס &amp; קסקט קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>כפיר אלקיים - תשאירי לי מקום לחבק אותך קאבר</v>
+        <v>צליל אבקסיס - לב לבן קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410776&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410853&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>כפיר אלקיים - תשאירי לי מקום לחבק אותך קאבר</v>
+        <v>צליל אבקסיס - לב לבן קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ינון אלהרר - אני לא מדונה קאבר</v>
+        <v>נתנאל אייל - מאשאפ תפילתו של ילד &amp; שמע ישראל</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410775&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410852&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ינון אלהרר - אני לא מדונה קאבר</v>
+        <v>נתנאל אייל - מאשאפ תפילתו של ילד &amp; שמע ישראל</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יגאל עדי - את לא שמה קאבר</v>
+        <v>נאור בן דוד - צעקתי בלילה קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410774&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410851&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יגאל עדי - את לא שמה קאבר</v>
+        <v>נאור בן דוד - צעקתי בלילה קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אלעד אביבי - עיניים עצובות קאבר</v>
+        <v>ליאם אוחיון - עיניים עצובות קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410773&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410850&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אלעד אביבי - עיניים עצובות קאבר</v>
+        <v>ליאם אוחיון - עיניים עצובות קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אליהו חזן - אני העבד קאבר</v>
+        <v>ליאור כהן - אהובה קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410772&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410849&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אליהו חזן - אני העבד קאבר</v>
+        <v>ליאור כהן - אהובה קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אילון לוי - ילדה מבורכת קאבר</v>
+        <v>יאיר פאיז &amp; איתמר פאיז - יא מחיג'ה + ישקף קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410771&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410848&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אילון לוי - ילדה מבורכת קאבר</v>
+        <v>יאיר פאיז &amp; איתמר פאיז - יא מחיג'ה + ישקף קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אדיר בוסטז &amp; יוסף מהצרי - לא אשכחך ירושלים קאבר</v>
+        <v>הקצב של המזרח - ציפור זרה קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410770&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410847&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אדיר בוסטז &amp; יוסף מהצרי - לא אשכחך ירושלים קאבר</v>
+        <v>הקצב של המזרח - ציפור זרה קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אבישי לוי - תמיד אמא קאבר</v>
+        <v>בן יוסף דניאל - לבד בינתיים קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410769&amp;sid=38b2f63fda389ed366df5f107dc8c300</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410846&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,12 +811,164 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אבישי לוי - תמיד אמא קאבר</v>
+        <v>בן יוסף דניאל - לבד בינתיים קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אסף פפל - איפה את קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410845&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אסף פפל - איפה את קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אלקנה שרביט - איזה מן עולם קאבר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410844&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אלקנה שרביט - איזה מן עולם קאבר</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אוהד חסקי - ברכת הכהנים קאבר</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410843&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אוהד חסקי - ברכת הכהנים קאבר</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אבישי עוזיאל - שום דבר ממך קאבר</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410842&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אבישי עוזיאל - שום דבר ממך קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תאי חבאני - נווה הדרים קאבר</v>
+        <v>שי מעברי - מחרוזת נער מתבגר &amp; רומיאו ויוליה 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410855&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410861&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-13</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תאי חבאני - נווה הדרים קאבר</v>
+        <v>שי מעברי - מחרוזת נער מתבגר &amp; רומיאו ויוליה 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קסם בל - רולקס &amp; קסקט קאבר</v>
+        <v>משה כהן - הללויה &amp; מזמור לתודה קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410854&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410860&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-13</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קסם בל - רולקס &amp; קסקט קאבר</v>
+        <v>משה כהן - הללויה &amp; מזמור לתודה קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>צליל אבקסיס - לב לבן קאבר</v>
+        <v>משה כהן - אהבת עולם קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410853&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410859&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-13</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>צליל אבקסיס - לב לבן קאבר</v>
+        <v>משה כהן - אהבת עולם קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נתנאל אייל - מאשאפ תפילתו של ילד &amp; שמע ישראל</v>
+        <v>ליאל דגן - מחרוזת כניסה לחופה 2026</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410852&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410858&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-13</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נתנאל אייל - מאשאפ תפילתו של ילד &amp; שמע ישראל</v>
+        <v>ליאל דגן - מחרוזת כניסה לחופה 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נאור בן דוד - צעקתי בלילה קאבר</v>
+        <v>ליאור כהן - תפילה קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410851&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410857&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-13</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נאור בן דוד - צעקתי בלילה קאבר</v>
+        <v>ליאור כהן - תפילה קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ליאם אוחיון - עיניים עצובות קאבר</v>
+        <v>יניב אדרי &amp; ברטין - מקלט בטוח קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-13</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410850&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410856&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-13</v>
@@ -659,316 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>ליאם אוחיון - עיניים עצובות קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ליאור כהן - אהובה קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410849&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>ליאור כהן - אהובה קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>יאיר פאיז &amp; איתמר פאיז - יא מחיג'ה + ישקף קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410848&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>יאיר פאיז &amp; איתמר פאיז - יא מחיג'ה + ישקף קאבר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>הקצב של המזרח - ציפור זרה קאבר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410847&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>הקצב של המזרח - ציפור זרה קאבר</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>בן יוסף דניאל - לבד בינתיים קאבר</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410846&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>בן יוסף דניאל - לבד בינתיים קאבר</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אסף פפל - איפה את קאבר</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410845&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אסף פפל - איפה את קאבר</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אלקנה שרביט - איזה מן עולם קאבר</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410844&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אלקנה שרביט - איזה מן עולם קאבר</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אוהד חסקי - ברכת הכהנים קאבר</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410843&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אוהד חסקי - ברכת הכהנים קאבר</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אבישי עוזיאל - שום דבר ממך קאבר</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410842&amp;sid=72965aab5296ce8e6991d14b6c144244</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אבישי עוזיאל - שום דבר ממך קאבר</v>
+        <v>יניב אדרי &amp; ברטין - מקלט בטוח קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שי מעברי - מחרוזת נער מתבגר &amp; רומיאו ויוליה 2026</v>
+        <v>נוריאל חדד - מה לך ילדה קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410861&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410865&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שי מעברי - מחרוזת נער מתבגר &amp; רומיאו ויוליה 2026</v>
+        <v>נוריאל חדד - מה לך ילדה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>משה כהן - הללויה &amp; מזמור לתודה קאבר</v>
+        <v>קובי יעקובוב - היית לי שקט קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410860&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410864&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>משה כהן - הללויה &amp; מזמור לתודה קאבר</v>
+        <v>קובי יעקובוב - היית לי שקט קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>משה כהן - אהבת עולם קאבר</v>
+        <v>לירז מדיזדה - חצי לב קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410859&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410863&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>משה כהן - אהבת עולם קאבר</v>
+        <v>לירז מדיזדה - חצי לב קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ליאל דגן - מחרוזת כניסה לחופה 2026</v>
+        <v>ינון אלהרר - עיניים עצובות קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410858&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410862&amp;sid=502df8379d68048e85461b9cb2f67ba8</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,88 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ליאל דגן - מחרוזת כניסה לחופה 2026</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ליאור כהן - תפילה קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410857&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>ליאור כהן - תפילה קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יניב אדרי &amp; ברטין - מקלט בטוח קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410856&amp;sid=204e335e55e221f2b2aff6dc1881b294</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יניב אדרי &amp; ברטין - מקלט בטוח קאבר</v>
+        <v>ינון אלהרר - עיניים עצובות קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>